--- a/artfynd/A 49375-2024 artfynd.xlsx
+++ b/artfynd/A 49375-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>110595334</v>
       </c>
       <c r="B2" t="n">
-        <v>85715</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515109.5114528873</v>
+        <v>515109</v>
       </c>
       <c r="R2" t="n">
-        <v>6944562.182170469</v>
+        <v>6944562</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,19 +746,9 @@
           <t>2023-07-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120617560</v>
+        <v>120617491</v>
       </c>
       <c r="B3" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515145</v>
+        <v>515054</v>
       </c>
       <c r="R3" t="n">
-        <v>6944386</v>
+        <v>6944335</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120617488</v>
+        <v>120617448</v>
       </c>
       <c r="B4" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -940,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515054</v>
+        <v>514977</v>
       </c>
       <c r="R4" t="n">
-        <v>6944335</v>
+        <v>6944602</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120617567</v>
+        <v>120617488</v>
       </c>
       <c r="B5" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515171</v>
+        <v>515054</v>
       </c>
       <c r="R5" t="n">
-        <v>6944514</v>
+        <v>6944335</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120617491</v>
+        <v>120617560</v>
       </c>
       <c r="B6" t="n">
-        <v>79676</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515054</v>
+        <v>515145</v>
       </c>
       <c r="R6" t="n">
-        <v>6944335</v>
+        <v>6944386</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120617448</v>
+        <v>120617567</v>
       </c>
       <c r="B7" t="n">
-        <v>79675</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1258,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514977</v>
+        <v>515171</v>
       </c>
       <c r="R7" t="n">
-        <v>6944602</v>
+        <v>6944514</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,112 +1278,6 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>120617468</v>
-      </c>
-      <c r="B8" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Julkvällsflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>515053</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6944344</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-10-11</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Erik Söderhjelm</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49375-2024 artfynd.xlsx
+++ b/artfynd/A 49375-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110595334</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617491</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617448</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617488</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617560</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,8 +1308,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617567</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>